--- a/kanban_system/output/library_linked/中东市场标准法规清单.xlsx
+++ b/kanban_system/output/library_linked/中东市场标准法规清单.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSO-已更新" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="草案" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沙特" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阿联酋" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伊朗" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伊拉克" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="约旦" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="叙利亚" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黎巴嫩、蒙古" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="GSO-已更新" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="草案" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="沙特" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="阿联酋" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="伊朗" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="伊拉克" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="约旦" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="叙利亚" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="黎巴嫩、蒙古" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="更新" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'GSO-已更新'!$A$1:$Y$1</definedName>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="G106" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H106" s="18" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="G119" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H119" s="18" t="inlineStr">

--- a/kanban_system/output/library_linked/中东市场标准法规清单.xlsx
+++ b/kanban_system/output/library_linked/中东市场标准法规清单.xlsx
@@ -28624,6 +28624,11 @@
           <t>引用自《与自动驾驶汽车技术法规实施相关的标准清单》</t>
         </is>
       </c>
+      <c r="Z62" s="41" t="inlineStr">
+        <is>
+          <t>INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="16.5" customHeight="1" s="39">
       <c r="A63" s="18" t="n">
